--- a/model_info/det_gemini_domain.xlsx
+++ b/model_info/det_gemini_domain.xlsx
@@ -344,7 +344,7 @@
     <col width="4.4" min="12" max="12" bestFit="1" customWidth="1"/>
     <col width="7.700000000000001" min="13" max="13" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="14" max="14" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="15" max="15" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="15" max="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -393,7 +393,7 @@
         <v>0.9745055239904677</v>
       </c>
       <c r="O1" s="0" t="n">
-        <v>0.2421875</v>
+        <v>0.62109375</v>
       </c>
     </row>
     <row r="2">
@@ -442,7 +442,7 @@
         <v>0.10256410256410256</v>
       </c>
       <c r="O2" s="0" t="n">
-        <v>0.014341085271317831</v>
+        <v>0.3563084736701417</v>
       </c>
     </row>
     <row r="3">
@@ -540,7 +540,7 @@
         <v>0.5064707161446439</v>
       </c>
       <c r="O4" s="0" t="n">
-        <v>0.42857142857142855</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="5">
@@ -638,7 +638,7 @@
         <v>0.47709913681079297</v>
       </c>
       <c r="O6" s="0" t="n">
-        <v>0.44444444444444453</v>
+        <v>0.7065972222222223</v>
       </c>
     </row>
     <row r="7">
@@ -736,7 +736,7 @@
         <v>0.9338106764140311</v>
       </c>
       <c r="O8" s="0" t="n">
-        <v>0.8452380952380952</v>
+        <v>0.9226190476190477</v>
       </c>
     </row>
     <row r="9">
@@ -834,7 +834,7 @@
         <v>0.7425955095750908</v>
       </c>
       <c r="O10" s="0" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.8541666666666667</v>
       </c>
     </row>
     <row r="11">
@@ -932,7 +932,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="O12" s="0" t="n">
-        <v>0.6662698412698412</v>
+        <v>0.8331349206349206</v>
       </c>
     </row>
     <row r="13">
@@ -1030,7 +1030,7 @@
         <v>1.0</v>
       </c>
       <c r="O14" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="15">
@@ -1177,7 +1177,7 @@
         <v>1.0</v>
       </c>
       <c r="O17" s="0" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9153846153846155</v>
       </c>
     </row>
     <row r="18">
@@ -1226,7 +1226,7 @@
         <v>0.9090909090909091</v>
       </c>
       <c r="O18" s="0" t="n">
-        <v>0.8783068783068783</v>
+        <v>0.8922784391534391</v>
       </c>
     </row>
     <row r="19">
@@ -1275,7 +1275,7 @@
         <v>0.45</v>
       </c>
       <c r="O19" s="0" t="n">
-        <v>0.34803921568627455</v>
+        <v>0.5724571078431373</v>
       </c>
     </row>
     <row r="20">
@@ -1324,7 +1324,7 @@
         <v>0.7692307692307693</v>
       </c>
       <c r="O20" s="0" t="n">
-        <v>0.8</v>
+        <v>0.8534883720930233</v>
       </c>
     </row>
     <row r="21">
@@ -1373,7 +1373,7 @@
         <v>0.9</v>
       </c>
       <c r="O21" s="0" t="n">
-        <v>0.66875</v>
+        <v>0.8040719696969697</v>
       </c>
     </row>
     <row r="22">
@@ -1422,7 +1422,7 @@
         <v>1.0</v>
       </c>
       <c r="O22" s="0" t="n">
-        <v>0.9226190476190477</v>
+        <v>0.9613095238095238</v>
       </c>
     </row>
   </sheetData>

--- a/model_info/det_gemini_domain.xlsx
+++ b/model_info/det_gemini_domain.xlsx
@@ -344,7 +344,7 @@
     <col width="4.4" min="12" max="12" bestFit="1" customWidth="1"/>
     <col width="7.700000000000001" min="13" max="13" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="14" max="14" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="15" max="15" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="15" max="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -393,7 +393,7 @@
         <v>0.9745055239904677</v>
       </c>
       <c r="O1" s="0" t="n">
-        <v>0.62109375</v>
+        <v>0.2421875</v>
       </c>
     </row>
     <row r="2">
@@ -442,7 +442,7 @@
         <v>0.10256410256410256</v>
       </c>
       <c r="O2" s="0" t="n">
-        <v>0.3563084736701417</v>
+        <v>0.010014033680834002</v>
       </c>
     </row>
     <row r="3">
@@ -540,7 +540,7 @@
         <v>0.5064707161446439</v>
       </c>
       <c r="O4" s="0" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.42857142857142855</v>
       </c>
     </row>
     <row r="5">
@@ -638,7 +638,7 @@
         <v>0.47709913681079297</v>
       </c>
       <c r="O6" s="0" t="n">
-        <v>0.7065972222222223</v>
+        <v>0.43055555555555564</v>
       </c>
     </row>
     <row r="7">
@@ -736,7 +736,7 @@
         <v>0.9338106764140311</v>
       </c>
       <c r="O8" s="0" t="n">
-        <v>0.9226190476190477</v>
+        <v>0.8452380952380952</v>
       </c>
     </row>
     <row r="9">
@@ -834,7 +834,7 @@
         <v>0.7425955095750908</v>
       </c>
       <c r="O10" s="0" t="n">
-        <v>0.8541666666666667</v>
+        <v>0.7083333333333334</v>
       </c>
     </row>
     <row r="11">
@@ -932,7 +932,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="O12" s="0" t="n">
-        <v>0.8331349206349206</v>
+        <v>0.6662698412698412</v>
       </c>
     </row>
     <row r="13">
@@ -1030,7 +1030,7 @@
         <v>1.0</v>
       </c>
       <c r="O14" s="0" t="n">
-        <v>0.8</v>
+        <v>0.6222222222222222</v>
       </c>
     </row>
     <row r="15">
@@ -1177,7 +1177,7 @@
         <v>1.0</v>
       </c>
       <c r="O17" s="0" t="n">
-        <v>0.9153846153846155</v>
+        <v>0.8376068376068376</v>
       </c>
     </row>
     <row r="18">
@@ -1226,7 +1226,7 @@
         <v>0.9090909090909091</v>
       </c>
       <c r="O18" s="0" t="n">
-        <v>0.8922784391534391</v>
+        <v>0.7959656084656084</v>
       </c>
     </row>
     <row r="19">
@@ -1275,7 +1275,7 @@
         <v>0.45</v>
       </c>
       <c r="O19" s="0" t="n">
-        <v>0.5724571078431373</v>
+        <v>0.27734375000000006</v>
       </c>
     </row>
     <row r="20">
@@ -1324,7 +1324,7 @@
         <v>0.7692307692307693</v>
       </c>
       <c r="O20" s="0" t="n">
-        <v>0.8534883720930233</v>
+        <v>0.7255813953488373</v>
       </c>
     </row>
     <row r="21">
@@ -1373,7 +1373,7 @@
         <v>0.9</v>
       </c>
       <c r="O21" s="0" t="n">
-        <v>0.8040719696969697</v>
+        <v>0.6282196969696969</v>
       </c>
     </row>
     <row r="22">
@@ -1422,7 +1422,7 @@
         <v>1.0</v>
       </c>
       <c r="O22" s="0" t="n">
-        <v>0.9613095238095238</v>
+        <v>0.9226190476190477</v>
       </c>
     </row>
   </sheetData>
